--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E373570-2557-46F2-ADAD-AD892E864FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E4EDE7-4E0E-40EB-BA8D-B5EC3A0744F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E4EDE7-4E0E-40EB-BA8D-B5EC3A0744F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3482E7D7-0AFE-4225-A8C5-F00E41E2E6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3482E7D7-0AFE-4225-A8C5-F00E41E2E6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C780B4C-203A-4B85-9C20-E50D062F35BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C780B4C-203A-4B85-9C20-E50D062F35BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2372C176-A218-44D8-8D0B-D5B15CCBFE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="109">
   <si>
     <t>C1</t>
   </si>
@@ -326,22 +326,10 @@
     <t>high</t>
   </si>
   <si>
-    <t>s1p1v1_d</t>
-  </si>
-  <si>
-    <t>s5p5v5_d</t>
-  </si>
-  <si>
-    <t>ts_annual</t>
-  </si>
-  <si>
     <t>pset_co</t>
   </si>
   <si>
     <t>e 1.5 deg no OS</t>
-  </si>
-  <si>
-    <t>d9d</t>
   </si>
   <si>
     <t>d 1.5 deg OS</t>
@@ -356,9 +344,6 @@
     <t>a 3 deg</t>
   </si>
   <si>
-    <t>c15d</t>
-  </si>
-  <si>
     <t>~Scenmap</t>
   </si>
   <si>
@@ -371,46 +356,7 @@
     <t>priority</t>
   </si>
   <si>
-    <t>ts_012</t>
-  </si>
-  <si>
-    <t>ts_048</t>
-  </si>
-  <si>
-    <t>ts_12t</t>
-  </si>
-  <si>
     <t>bio price multiplier</t>
-  </si>
-  <si>
-    <t>s1v1_d</t>
-  </si>
-  <si>
-    <t>ts_030</t>
-  </si>
-  <si>
-    <t>f2d96</t>
-  </si>
-  <si>
-    <t>ts_096</t>
-  </si>
-  <si>
-    <t>e96</t>
-  </si>
-  <si>
-    <t>ts_072</t>
-  </si>
-  <si>
-    <t>ts_144</t>
-  </si>
-  <si>
-    <t>ts_288</t>
-  </si>
-  <si>
-    <t>x12</t>
-  </si>
-  <si>
-    <t>xAnn</t>
   </si>
   <si>
     <t>R10EUROPE</t>
@@ -428,9 +374,6 @@
     <t>heat_tfc_twh</t>
   </si>
   <si>
-    <t>HET</t>
-  </si>
-  <si>
     <t>1-8</t>
   </si>
   <si>
@@ -444,6 +387,12 @@
   </si>
   <si>
     <t>HRV</t>
+  </si>
+  <si>
+    <t>het_industry</t>
+  </si>
+  <si>
+    <t>het_buildings</t>
   </si>
   <si>
     <t>Krk LNG, forest resources</t>
@@ -882,7 +831,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$O$17:$U$17</c:f>
+              <c:f>Veda!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -912,7 +861,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$O$14:$U$14</c:f>
+              <c:f>Veda!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1170,7 +1119,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$D$17:$J$17</c:f>
+              <c:f>Veda!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1200,7 +1149,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$D$24:$J$24</c:f>
+              <c:f>Veda!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1395,13 +1344,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>481012</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>250032</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5984,7 +5933,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G1" s="16" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
@@ -6010,24 +5959,24 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -6042,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E9" s="14">
         <v>0</v>
@@ -6061,7 +6010,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E10" s="14">
         <v>100</v>
@@ -6080,7 +6029,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E11" s="14">
         <v>200</v>
@@ -6099,7 +6048,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E12" s="14">
         <v>300</v>
@@ -6205,7 +6154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH85"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.59765625" customWidth="1"/>
@@ -6226,13 +6175,13 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.45">
       <c r="A1" s="15" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.45">
       <c r="A2" s="15" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>25</v>
@@ -6251,7 +6200,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>7</v>
@@ -6289,30 +6238,18 @@
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.45">
       <c r="AH8" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.45">
       <c r="N9" t="s">
         <v>4</v>
       </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE9" s="10">
-        <v>1</v>
-      </c>
       <c r="AF9" t="s">
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AH9" s="12">
         <v>5</v>
@@ -6322,23 +6259,11 @@
       <c r="N10" s="1">
         <v>2022</v>
       </c>
-      <c r="AB10">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE10" s="10">
-        <v>1</v>
-      </c>
       <c r="AF10" t="s">
         <v>2</v>
       </c>
       <c r="AG10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AH10" s="12">
         <v>4</v>
@@ -6346,30 +6271,17 @@
     </row>
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
-        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O28-O29</f>
+        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
         <v>18.810000000000002</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AB11">
-        <v>3</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD11" t="str">
-        <f>AC11</f>
-        <v>ts_012</v>
-      </c>
-      <c r="AE11" s="10">
-        <v>1</v>
-      </c>
       <c r="AF11" t="s">
         <v>5</v>
       </c>
       <c r="AG11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AH11" s="12">
         <v>3</v>
@@ -6377,1529 +6289,1142 @@
     </row>
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
-        <f>SUMIFS(iea_data!J3:J9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>3.5720000000000001</v>
-      </c>
-      <c r="AB12">
-        <v>4</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD12" t="str">
-        <f t="shared" ref="AD12:AD16" si="0">AC12</f>
-        <v>ts_030</v>
-      </c>
-      <c r="AE12" s="10">
-        <v>1</v>
+        <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>0.95899999999999996</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
       </c>
       <c r="AG12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AH12" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="AB13">
-        <v>5</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD13" t="str">
-        <f t="shared" si="0"/>
-        <v>ts_048</v>
-      </c>
-      <c r="AE13" s="10">
-        <v>1</v>
+    <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="N13" s="17">
+        <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>1.927</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
       </c>
       <c r="AG13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AH13" s="12">
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" t="s">
+    <row r="14" spans="1:34" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="15" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C15" s="3" t="str">
         <f>VLOOKUP(controller!$D$5,$I$3:$J$5,2,FALSE)</f>
         <v>C4</v>
       </c>
-      <c r="D14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="D15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.05</v>
       </c>
-      <c r="F14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="F15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.17</v>
       </c>
-      <c r="G14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="G15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.29</v>
       </c>
-      <c r="H14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="H15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.42</v>
       </c>
-      <c r="I14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="I15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.59</v>
       </c>
-      <c r="J14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="J15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.73</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O15" s="8">
         <f>N11</f>
         <v>18.810000000000002</v>
       </c>
-      <c r="P14" s="8">
-        <f t="shared" ref="P14:U14" si="1">$N$11*E14</f>
+      <c r="P15" s="8">
+        <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
         <v>19.750500000000002</v>
       </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="1"/>
+      <c r="Q15" s="8">
+        <f t="shared" si="0"/>
         <v>22.0077</v>
       </c>
-      <c r="R14" s="8">
-        <f t="shared" si="1"/>
+      <c r="R15" s="8">
+        <f t="shared" si="0"/>
         <v>24.264900000000004</v>
       </c>
-      <c r="S14" s="8">
-        <f t="shared" si="1"/>
+      <c r="S15" s="8">
+        <f t="shared" si="0"/>
         <v>26.7102</v>
       </c>
-      <c r="T14" s="8">
-        <f t="shared" si="1"/>
+      <c r="T15" s="8">
+        <f t="shared" si="0"/>
         <v>29.907900000000005</v>
       </c>
-      <c r="U14" s="8">
-        <f t="shared" si="1"/>
+      <c r="U15" s="8">
+        <f t="shared" si="0"/>
         <v>32.541300000000007</v>
       </c>
-      <c r="AB14">
-        <v>6</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD14" t="str">
-        <f t="shared" si="0"/>
-        <v>ts_072</v>
-      </c>
-      <c r="AE14" s="10">
-        <f>AE9+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+    </row>
+    <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>0.98</v>
       </c>
-      <c r="F15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="F16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>0.96</v>
       </c>
-      <c r="G15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="G16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>0.92</v>
       </c>
-      <c r="H15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="H16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>0.84</v>
       </c>
-      <c r="I15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="I16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>0.83</v>
       </c>
-      <c r="J15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="J16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>0.8</v>
       </c>
-      <c r="AB15">
-        <v>7</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>107</v>
-      </c>
-      <c r="AD15" t="str">
-        <f t="shared" si="0"/>
-        <v>ts_144</v>
-      </c>
-      <c r="AE15" s="10">
-        <f t="shared" ref="AE15:AE78" si="2">AE10+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="N16" s="5" t="str">
+    </row>
+    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=HRV</v>
       </c>
-      <c r="AB16">
-        <v>8</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD16" t="str">
-        <f t="shared" si="0"/>
-        <v>ts_288</v>
-      </c>
-      <c r="AE16" s="10">
+    </row>
+    <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D18" s="7">
+        <v>2020</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" ref="E18:J18" si="1">P18</f>
+        <v>2025</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="1"/>
+        <v>2035</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="1"/>
+        <v>2040</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="1"/>
+        <v>2045</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="1"/>
+        <v>2050</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="4">
+        <v>2022</v>
+      </c>
+      <c r="P18" s="4">
+        <v>2025</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>2030</v>
+      </c>
+      <c r="R18" s="4">
+        <v>2035</v>
+      </c>
+      <c r="S18" s="4">
+        <v>2040</v>
+      </c>
+      <c r="T18" s="4">
+        <v>2045</v>
+      </c>
+      <c r="U18" s="4">
+        <v>2050</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="6">
+        <f t="shared" ref="O19:U21" si="2">D19*O$15</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:31" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D17" s="7">
-        <v>2020</v>
-      </c>
-      <c r="E17" s="7">
-        <f t="shared" ref="E17:J17" si="3">P17</f>
-        <v>2025</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="3"/>
-        <v>2030</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="3"/>
-        <v>2035</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="3"/>
-        <v>2040</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="3"/>
-        <v>2045</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="3"/>
-        <v>2050</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O17" s="4">
-        <v>2022</v>
-      </c>
-      <c r="P17" s="4">
-        <v>2025</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>2030</v>
-      </c>
-      <c r="R17" s="4">
-        <v>2035</v>
-      </c>
-      <c r="S17" s="4">
-        <v>2040</v>
-      </c>
-      <c r="T17" s="4">
-        <v>2045</v>
-      </c>
-      <c r="U17" s="4">
-        <v>2050</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB17">
-        <v>9</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="O18" s="6">
-        <f t="shared" ref="O18:U20" si="4">D18*O$14</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V18" t="s">
-        <v>16</v>
-      </c>
-      <c r="X18" s="2"/>
-      <c r="AB18">
-        <v>10</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>105</v>
-      </c>
-      <c r="AE18" s="10">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.37</v>
-      </c>
-      <c r="E19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.35</v>
-      </c>
-      <c r="F19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.34</v>
-      </c>
-      <c r="G19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.33</v>
-      </c>
-      <c r="H19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.3</v>
-      </c>
-      <c r="I19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="J19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.3</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" s="6">
-        <f t="shared" si="4"/>
-        <v>6.9597000000000007</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" si="4"/>
-        <v>6.9126750000000001</v>
-      </c>
-      <c r="Q19" s="6">
-        <f t="shared" si="4"/>
-        <v>7.4826180000000004</v>
-      </c>
-      <c r="R19" s="6">
-        <f t="shared" si="4"/>
-        <v>8.007417000000002</v>
+        <v>0</v>
       </c>
       <c r="S19" s="6">
-        <f t="shared" si="4"/>
-        <v>8.0130599999999994</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="T19" s="6">
-        <f t="shared" si="4"/>
-        <v>8.6732910000000007</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U19" s="6">
-        <f t="shared" si="4"/>
-        <v>9.7623900000000017</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="V19" t="s">
         <v>16</v>
       </c>
-      <c r="AB19">
-        <v>11</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE19" s="10">
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.37</v>
+      </c>
+      <c r="E20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.35</v>
+      </c>
+      <c r="F20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.34</v>
+      </c>
+      <c r="G20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.33</v>
+      </c>
+      <c r="H20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.3</v>
+      </c>
+      <c r="I20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.3</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.59</v>
-      </c>
-      <c r="E20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.59</v>
-      </c>
-      <c r="F20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.59</v>
-      </c>
-      <c r="G20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="H20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="I20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.54</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="6">
-        <f t="shared" si="4"/>
-        <v>11.097900000000001</v>
+        <v>6.9597000000000007</v>
       </c>
       <c r="P20" s="6">
-        <f t="shared" si="4"/>
-        <v>11.652795000000001</v>
+        <f t="shared" si="2"/>
+        <v>6.9126750000000001</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="4"/>
-        <v>12.984542999999999</v>
+        <f t="shared" si="2"/>
+        <v>7.4826180000000004</v>
       </c>
       <c r="R20" s="6">
-        <f t="shared" si="4"/>
-        <v>14.073642000000001</v>
+        <f t="shared" si="2"/>
+        <v>8.007417000000002</v>
       </c>
       <c r="S20" s="6">
-        <f t="shared" si="4"/>
-        <v>15.491916</v>
+        <f t="shared" si="2"/>
+        <v>8.0130599999999994</v>
       </c>
       <c r="T20" s="6">
-        <f t="shared" si="4"/>
-        <v>16.748424000000004</v>
+        <f t="shared" si="2"/>
+        <v>8.6732910000000007</v>
       </c>
       <c r="U20" s="6">
-        <f t="shared" si="4"/>
-        <v>17.572302000000004</v>
+        <f t="shared" si="2"/>
+        <v>9.7623900000000017</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
       </c>
-      <c r="AB20">
-        <v>12</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE20" s="10">
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.59</v>
+      </c>
+      <c r="E21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.59</v>
+      </c>
+      <c r="F21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.59</v>
+      </c>
+      <c r="G21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.54</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.03</v>
-      </c>
-      <c r="E21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.05</v>
-      </c>
-      <c r="F21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.04</v>
-      </c>
-      <c r="G21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.06</v>
-      </c>
-      <c r="H21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="I21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.08</v>
-      </c>
-      <c r="J21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.08</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" s="6">
-        <f>D21*O$14</f>
-        <v>0.56430000000000002</v>
+        <v>11.097900000000001</v>
       </c>
       <c r="P21" s="6">
-        <f t="shared" ref="P21:U21" si="5">O21</f>
-        <v>0.56430000000000002</v>
+        <f t="shared" si="2"/>
+        <v>11.652795000000001</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="5"/>
-        <v>0.56430000000000002</v>
+        <f t="shared" si="2"/>
+        <v>12.984542999999999</v>
       </c>
       <c r="R21" s="6">
-        <f t="shared" si="5"/>
-        <v>0.56430000000000002</v>
+        <f t="shared" si="2"/>
+        <v>14.073642000000001</v>
       </c>
       <c r="S21" s="6">
-        <f t="shared" si="5"/>
-        <v>0.56430000000000002</v>
+        <f t="shared" si="2"/>
+        <v>15.491916</v>
       </c>
       <c r="T21" s="6">
-        <f t="shared" si="5"/>
-        <v>0.56430000000000002</v>
+        <f t="shared" si="2"/>
+        <v>16.748424000000004</v>
       </c>
       <c r="U21" s="6">
-        <f t="shared" si="5"/>
-        <v>0.56430000000000002</v>
+        <f t="shared" si="2"/>
+        <v>17.572302000000004</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE21" s="10">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:31" x14ac:dyDescent="0.45">
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.03</v>
+      </c>
+      <c r="E22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.05</v>
+      </c>
+      <c r="F22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.04</v>
+      </c>
+      <c r="G22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.06</v>
+      </c>
+      <c r="H22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.08</v>
+      </c>
+      <c r="J22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.08</v>
+      </c>
       <c r="N22" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O22" s="6">
-        <f t="shared" ref="O22:U22" si="6">O14-SUM(O19:O21)</f>
-        <v>0.18810000000000215</v>
+        <f>D22*O$15</f>
+        <v>0.56430000000000002</v>
       </c>
       <c r="P22" s="6">
-        <f t="shared" si="6"/>
-        <v>0.62073000000000178</v>
+        <f t="shared" ref="P22:U22" si="3">O22</f>
+        <v>0.56430000000000002</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" si="6"/>
-        <v>0.97623900000000319</v>
+        <f t="shared" si="3"/>
+        <v>0.56430000000000002</v>
       </c>
       <c r="R22" s="6">
-        <f t="shared" si="6"/>
-        <v>1.6195410000000017</v>
+        <f t="shared" si="3"/>
+        <v>0.56430000000000002</v>
       </c>
       <c r="S22" s="6">
-        <f t="shared" si="6"/>
-        <v>2.6409240000000018</v>
+        <f t="shared" si="3"/>
+        <v>0.56430000000000002</v>
       </c>
       <c r="T22" s="6">
-        <f t="shared" si="6"/>
-        <v>3.9218849999999996</v>
+        <f t="shared" si="3"/>
+        <v>0.56430000000000002</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" si="6"/>
-        <v>4.6423080000000034</v>
+        <f t="shared" si="3"/>
+        <v>0.56430000000000002</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
       </c>
-      <c r="AE22" s="10">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="N23" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="O23" s="19">
+      <c r="X22" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="N23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
+        <v>0.18810000000000215</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="4"/>
+        <v>0.62073000000000178</v>
+      </c>
+      <c r="Q23" s="6">
+        <f t="shared" si="4"/>
+        <v>0.97623900000000319</v>
+      </c>
+      <c r="R23" s="6">
+        <f t="shared" si="4"/>
+        <v>1.6195410000000017</v>
+      </c>
+      <c r="S23" s="6">
+        <f t="shared" si="4"/>
+        <v>2.6409240000000018</v>
+      </c>
+      <c r="T23" s="6">
+        <f t="shared" si="4"/>
+        <v>3.9218849999999996</v>
+      </c>
+      <c r="U23" s="6">
+        <f t="shared" si="4"/>
+        <v>4.6423080000000034</v>
+      </c>
+      <c r="V23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="N24" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="O24" s="19">
         <f>N12</f>
-        <v>3.5720000000000001</v>
-      </c>
-      <c r="P23" s="20">
-        <f>$N$12*E15</f>
-        <v>3.5005600000000001</v>
-      </c>
-      <c r="Q23" s="20">
-        <f>$N$12*F15</f>
-        <v>3.4291199999999997</v>
-      </c>
-      <c r="R23" s="20">
-        <f t="shared" ref="R23:U23" si="7">$N$12*G15</f>
-        <v>3.2862400000000003</v>
-      </c>
-      <c r="S23" s="20">
-        <f t="shared" si="7"/>
-        <v>3.00048</v>
-      </c>
-      <c r="T23" s="20">
-        <f t="shared" si="7"/>
-        <v>2.9647600000000001</v>
-      </c>
-      <c r="U23" s="20">
-        <f t="shared" si="7"/>
-        <v>2.8576000000000001</v>
-      </c>
-      <c r="V23" s="18" t="s">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="P24" s="20">
+        <f>$N$12*E16</f>
+        <v>0.93981999999999999</v>
+      </c>
+      <c r="Q24" s="20">
+        <f>$N$12*F16</f>
+        <v>0.9206399999999999</v>
+      </c>
+      <c r="R24" s="20">
+        <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
+        <v>0.88227999999999995</v>
+      </c>
+      <c r="S24" s="20">
+        <f t="shared" si="5"/>
+        <v>0.80555999999999994</v>
+      </c>
+      <c r="T24" s="20">
+        <f t="shared" si="5"/>
+        <v>0.79596999999999996</v>
+      </c>
+      <c r="U24" s="20">
+        <f t="shared" si="5"/>
+        <v>0.76719999999999999</v>
+      </c>
+      <c r="V24" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="AE23" s="10">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:31" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="10" t="s">
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="N25" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="O25" s="19">
+        <f>N13</f>
+        <v>1.927</v>
+      </c>
+      <c r="P25" s="20">
+        <f>$N$13*E16</f>
+        <v>1.88846</v>
+      </c>
+      <c r="Q25" s="20">
+        <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
+        <v>1.84992</v>
+      </c>
+      <c r="R25" s="20">
+        <f t="shared" si="6"/>
+        <v>1.7728400000000002</v>
+      </c>
+      <c r="S25" s="20">
+        <f t="shared" si="6"/>
+        <v>1.6186799999999999</v>
+      </c>
+      <c r="T25" s="20">
+        <f t="shared" si="6"/>
+        <v>1.59941</v>
+      </c>
+      <c r="U25" s="20">
+        <f t="shared" si="6"/>
+        <v>1.5416000000000001</v>
+      </c>
+      <c r="V25" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B26" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C26" s="3" t="str">
         <f>VLOOKUP(controller!E5,$F$3:$G$6,2,FALSE)</f>
         <v>C3</v>
       </c>
-      <c r="D24" s="8">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>71.48</v>
       </c>
-      <c r="G24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="G26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>104.42</v>
       </c>
-      <c r="H24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="H26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>134.85</v>
       </c>
-      <c r="I24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="I26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>178.1</v>
       </c>
-      <c r="J24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="J26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>209.45</v>
       </c>
-      <c r="N24" s="21" t="s">
+      <c r="N26" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="23">
-        <f>F24/1000</f>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="23">
+        <f>F26/1000</f>
         <v>7.1480000000000002E-2</v>
       </c>
-      <c r="R24" s="23">
-        <f>G24/1000</f>
+      <c r="R26" s="23">
+        <f>G26/1000</f>
         <v>0.10442</v>
       </c>
-      <c r="S24" s="23">
-        <f>H24/1000</f>
+      <c r="S26" s="23">
+        <f>H26/1000</f>
         <v>0.13485</v>
       </c>
-      <c r="T24" s="23">
-        <f>I24/1000</f>
+      <c r="T26" s="23">
+        <f>I26/1000</f>
         <v>0.17809999999999998</v>
       </c>
-      <c r="U24" s="23">
-        <f>J24/1000</f>
+      <c r="U26" s="23">
+        <f>J26/1000</f>
         <v>0.20945</v>
       </c>
-      <c r="V24" s="24" t="s">
+      <c r="V26" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AE24" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="2:31" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="AE25" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="2:31" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="N26" s="5" t="str">
+    </row>
+    <row r="27" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=HRV</v>
       </c>
-      <c r="AE26" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="2:31" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="N27" s="4" t="s">
+    </row>
+    <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="N29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O27" s="4">
-        <f t="shared" ref="O27:U27" si="8">O17</f>
+      <c r="O29" s="4">
+        <f t="shared" ref="O29:U29" si="7">O18</f>
         <v>2022</v>
       </c>
-      <c r="P27" s="4">
-        <f t="shared" si="8"/>
+      <c r="P29" s="4">
+        <f t="shared" si="7"/>
         <v>2025</v>
       </c>
-      <c r="Q27" s="4">
-        <f t="shared" si="8"/>
+      <c r="Q29" s="4">
+        <f t="shared" si="7"/>
         <v>2030</v>
       </c>
-      <c r="R27" s="4">
+      <c r="R29" s="4">
+        <f t="shared" si="7"/>
+        <v>2035</v>
+      </c>
+      <c r="S29" s="4">
+        <f t="shared" si="7"/>
+        <v>2040</v>
+      </c>
+      <c r="T29" s="4">
+        <f t="shared" si="7"/>
+        <v>2045</v>
+      </c>
+      <c r="U29" s="4">
+        <f t="shared" si="7"/>
+        <v>2050</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="L30" s="3">
+        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>11.92</v>
+      </c>
+      <c r="N30" t="s">
+        <v>30</v>
+      </c>
+      <c r="O30" s="3">
+        <f>L30</f>
+        <v>11.92</v>
+      </c>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" t="s">
+        <v>31</v>
+      </c>
+      <c r="W30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="L31" s="3">
+        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>-7.22</v>
+      </c>
+      <c r="N31" t="s">
+        <v>33</v>
+      </c>
+      <c r="O31" s="3">
+        <f>-1*L31</f>
+        <v>7.22</v>
+      </c>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" t="s">
+        <v>31</v>
+      </c>
+      <c r="W31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.07</v>
+      </c>
+      <c r="F39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.24</v>
+      </c>
+      <c r="G39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.25</v>
+      </c>
+      <c r="I39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.17</v>
+      </c>
+      <c r="J39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.02</v>
+      </c>
+      <c r="F40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.06</v>
+      </c>
+      <c r="G40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.07</v>
+      </c>
+      <c r="H40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.08</v>
+      </c>
+      <c r="I40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.01</v>
+      </c>
+      <c r="F41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="G41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.01</v>
+      </c>
+      <c r="H41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.01</v>
+      </c>
+      <c r="I41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.04</v>
+      </c>
+      <c r="J41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.96</v>
+      </c>
+      <c r="F42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.04</v>
+      </c>
+      <c r="G42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.04</v>
+      </c>
+      <c r="H42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.98</v>
+      </c>
+      <c r="I42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.99</v>
+      </c>
+      <c r="J42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B45" s="5" t="str">
+        <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
+        <v>~TFM_INS-TS: region=HRV; attribute=flo_cost;pset_pn=-IMP*Z</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46">
+        <v>2022</v>
+      </c>
+      <c r="E46">
+        <f>E18</f>
+        <v>2025</v>
+      </c>
+      <c r="F46">
+        <f t="shared" ref="F46:J46" si="8">F18</f>
+        <v>2030</v>
+      </c>
+      <c r="G46">
         <f t="shared" si="8"/>
         <v>2035</v>
       </c>
-      <c r="S27" s="4">
+      <c r="H46">
         <f t="shared" si="8"/>
         <v>2040</v>
       </c>
-      <c r="T27" s="4">
+      <c r="I46">
         <f t="shared" si="8"/>
         <v>2045</v>
       </c>
-      <c r="U27" s="4">
+      <c r="J46">
         <f t="shared" si="8"/>
         <v>2050</v>
       </c>
-      <c r="V27" s="4" t="s">
+      <c r="M46" t="s">
+        <v>80</v>
+      </c>
+      <c r="N46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" t="str">
+        <f>B47</f>
+        <v>Gas</v>
+      </c>
+      <c r="D47">
+        <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
+        <v>33.4</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="9"/>
+        <v>35.738</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="9"/>
+        <v>41.415999999999997</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="9"/>
+        <v>38.409999999999997</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="9"/>
+        <v>41.75</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="9"/>
+        <v>39.077999999999996</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="9"/>
+        <v>44.756</v>
+      </c>
+      <c r="M47">
+        <f>HLOOKUP($B47&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>27.4</v>
+      </c>
+      <c r="N47">
+        <f>HLOOKUP($B47&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" ref="C48:C50" si="10">B48</f>
+        <v>Coal</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="9"/>
+        <v>13.7</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="9"/>
+        <v>13.974</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="9"/>
+        <v>14.522</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="9"/>
+        <v>14.659000000000001</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="9"/>
+        <v>14.795999999999999</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="9"/>
+        <v>15.07</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="9"/>
+        <v>15.344000000000001</v>
+      </c>
+      <c r="M48">
+        <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>12.2</v>
+      </c>
+      <c r="N48">
+        <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="10"/>
+        <v>Oil</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="9"/>
+        <v>53</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="9"/>
+        <v>53.53</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="9"/>
+        <v>58.830000000000005</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="9"/>
+        <v>53.53</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="9"/>
+        <v>53.53</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="9"/>
+        <v>55.120000000000005</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="9"/>
+        <v>60.419999999999995</v>
+      </c>
+      <c r="M49">
+        <f>HLOOKUP($B49&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>48</v>
+      </c>
+      <c r="N49">
+        <f>HLOOKUP($B49&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="10"/>
+        <v>Bioenergy</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="9"/>
+        <v>26</v>
+      </c>
+      <c r="J50">
+        <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
+        <v>78</v>
+      </c>
+      <c r="M50">
+        <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>22</v>
+      </c>
+      <c r="N50">
+        <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55">
+        <v>2024</v>
+      </c>
+      <c r="D55">
+        <v>2030</v>
+      </c>
+      <c r="E55">
+        <v>2040</v>
+      </c>
+      <c r="F55" t="s">
         <v>13</v>
       </c>
-      <c r="W27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE27" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="2:31" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="L28" s="3">
-        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>11.92</v>
-      </c>
-      <c r="N28" t="s">
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56">
+        <v>3.3</v>
+      </c>
+      <c r="D56">
+        <v>2.6</v>
+      </c>
+      <c r="E56">
+        <v>2.7</v>
+      </c>
+      <c r="F56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
         <v>30</v>
       </c>
-      <c r="O28" s="3">
-        <f>L28</f>
-        <v>11.92</v>
-      </c>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" t="s">
-        <v>31</v>
-      </c>
-      <c r="W28" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE28" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="2:31" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="L29" s="3">
-        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>-7.22</v>
-      </c>
-      <c r="N29" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" s="3">
-        <f>-1*L29</f>
-        <v>7.22</v>
-      </c>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" t="s">
-        <v>31</v>
-      </c>
-      <c r="W29" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE29" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:31" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="AE30" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="AE31" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="AE32" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="AE33" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="AE34" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="AE35" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE36" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.07</v>
-      </c>
-      <c r="F37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.24</v>
-      </c>
-      <c r="G37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="H37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.25</v>
-      </c>
-      <c r="I37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.17</v>
-      </c>
-      <c r="J37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.34</v>
-      </c>
-      <c r="AE37" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.02</v>
-      </c>
-      <c r="F38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.06</v>
-      </c>
-      <c r="G38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.07</v>
-      </c>
-      <c r="H38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.08</v>
-      </c>
-      <c r="I38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="AE38" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.01</v>
-      </c>
-      <c r="F39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="G39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.01</v>
-      </c>
-      <c r="H39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.01</v>
-      </c>
-      <c r="I39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.04</v>
-      </c>
-      <c r="J39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="AE39" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.96</v>
-      </c>
-      <c r="F40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.04</v>
-      </c>
-      <c r="G40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.04</v>
-      </c>
-      <c r="H40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.98</v>
-      </c>
-      <c r="I40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.99</v>
-      </c>
-      <c r="J40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="AE40" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="AE41" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="AE42" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B43" s="5" t="str">
-        <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=HRV; attribute=flo_cost;pset_pn=-IMP*Z</v>
-      </c>
-      <c r="AE43" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44">
-        <v>2022</v>
-      </c>
-      <c r="E44">
-        <f>E17</f>
-        <v>2025</v>
-      </c>
-      <c r="F44">
-        <f t="shared" ref="F44:J44" si="9">F17</f>
-        <v>2030</v>
-      </c>
-      <c r="G44">
-        <f t="shared" si="9"/>
-        <v>2035</v>
-      </c>
-      <c r="H44">
-        <f t="shared" si="9"/>
-        <v>2040</v>
-      </c>
-      <c r="I44">
-        <f t="shared" si="9"/>
-        <v>2045</v>
-      </c>
-      <c r="J44">
-        <f t="shared" si="9"/>
-        <v>2050</v>
-      </c>
-      <c r="M44" t="s">
-        <v>80</v>
-      </c>
-      <c r="N44" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE44" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" t="str">
-        <f>B45</f>
-        <v>Gas</v>
-      </c>
-      <c r="D45">
-        <f t="shared" ref="D45:J48" si="10">AVERAGE($M45:$N45)*D37</f>
-        <v>33.4</v>
-      </c>
-      <c r="E45">
-        <f t="shared" si="10"/>
-        <v>35.738</v>
-      </c>
-      <c r="F45">
-        <f t="shared" si="10"/>
-        <v>41.415999999999997</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="10"/>
-        <v>38.409999999999997</v>
-      </c>
-      <c r="H45">
-        <f t="shared" si="10"/>
-        <v>41.75</v>
-      </c>
-      <c r="I45">
-        <f t="shared" si="10"/>
-        <v>39.077999999999996</v>
-      </c>
-      <c r="J45">
-        <f t="shared" si="10"/>
-        <v>44.756</v>
-      </c>
-      <c r="M45">
-        <f>HLOOKUP($B45&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>27.4</v>
-      </c>
-      <c r="N45">
-        <f>HLOOKUP($B45&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>39.4</v>
-      </c>
-      <c r="AE45" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" t="str">
-        <f t="shared" ref="C46:C48" si="11">B46</f>
-        <v>Coal</v>
-      </c>
-      <c r="D46">
-        <f t="shared" si="10"/>
-        <v>13.7</v>
-      </c>
-      <c r="E46">
-        <f t="shared" si="10"/>
-        <v>13.974</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="10"/>
-        <v>14.522</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="10"/>
-        <v>14.659000000000001</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="10"/>
-        <v>14.795999999999999</v>
-      </c>
-      <c r="I46">
-        <f t="shared" si="10"/>
-        <v>15.07</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="10"/>
-        <v>15.344000000000001</v>
-      </c>
-      <c r="M46">
-        <f>HLOOKUP($B46&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>12.2</v>
-      </c>
-      <c r="N46">
-        <f>HLOOKUP($B46&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>15.2</v>
-      </c>
-      <c r="AE46" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" t="str">
-        <f t="shared" si="11"/>
-        <v>Oil</v>
-      </c>
-      <c r="D47">
-        <f t="shared" si="10"/>
-        <v>53</v>
-      </c>
-      <c r="E47">
-        <f t="shared" si="10"/>
-        <v>53.53</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="10"/>
-        <v>58.830000000000005</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="10"/>
-        <v>53.53</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="10"/>
-        <v>53.53</v>
-      </c>
-      <c r="I47">
-        <f t="shared" si="10"/>
-        <v>55.120000000000005</v>
-      </c>
-      <c r="J47">
-        <f t="shared" si="10"/>
-        <v>60.419999999999995</v>
-      </c>
-      <c r="M47">
-        <f>HLOOKUP($B47&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>48</v>
-      </c>
-      <c r="N47">
-        <f>HLOOKUP($B47&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>58</v>
-      </c>
-      <c r="AE47" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" t="str">
-        <f t="shared" si="11"/>
-        <v>Bioenergy</v>
-      </c>
-      <c r="D48">
-        <f t="shared" si="10"/>
-        <v>26</v>
-      </c>
-      <c r="J48">
-        <f>VLOOKUP($C$14,$AF$9:$AH$15,3,FALSE)*D48</f>
-        <v>78</v>
-      </c>
-      <c r="M48">
-        <f>HLOOKUP($B48&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>22</v>
-      </c>
-      <c r="N48">
-        <f>HLOOKUP($B48&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="AE48" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE49" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE50" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE51" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE52" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE53" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE54" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE55" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE56" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE57" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE58" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE59" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE60" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE61" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE62" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE63" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE64" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE65" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE66" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE67" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE68" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE69" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE70" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE71" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE72" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE73" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE74" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE75" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE76" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE77" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78" spans="31:31" x14ac:dyDescent="0.45">
-      <c r="AE78" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>28</v>
-      </c>
-      <c r="B83" t="s">
-        <v>29</v>
-      </c>
-      <c r="C83">
-        <v>2024</v>
-      </c>
-      <c r="D83">
-        <v>2030</v>
-      </c>
-      <c r="E83">
-        <v>2040</v>
-      </c>
-      <c r="F83" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>33</v>
-      </c>
-      <c r="B84" t="s">
-        <v>124</v>
-      </c>
-      <c r="C84">
-        <v>3.3</v>
-      </c>
-      <c r="D84">
-        <v>2.6</v>
-      </c>
-      <c r="E84">
-        <v>2.7</v>
-      </c>
-      <c r="F84" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>30</v>
-      </c>
-      <c r="B85" t="s">
-        <v>124</v>
-      </c>
-      <c r="C85">
+      <c r="B57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57">
         <v>1.2</v>
       </c>
-      <c r="D85">
+      <c r="D57">
         <v>0.9</v>
       </c>
-      <c r="E85">
+      <c r="E57">
         <v>1.544</v>
       </c>
-      <c r="F85" t="s">
-        <v>125</v>
+      <c r="F57" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -7961,7 +7486,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B11">
         <v>27.4</v>
@@ -7988,7 +7513,7 @@
         <v>30</v>
       </c>
       <c r="J11" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -8048,21 +7573,21 @@
         <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="L10" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B11">
         <v>2000</v>
@@ -8103,7 +7628,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B12">
         <v>2001</v>
@@ -8144,7 +7669,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B13">
         <v>2002</v>
@@ -8185,7 +7710,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B14">
         <v>2003</v>
@@ -8226,7 +7751,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B15">
         <v>2004</v>
@@ -8267,7 +7792,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B16">
         <v>2005</v>
@@ -8308,7 +7833,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B17">
         <v>2006</v>
@@ -8349,7 +7874,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B18">
         <v>2007</v>
@@ -8390,7 +7915,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B19">
         <v>2008</v>
@@ -8431,7 +7956,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B20">
         <v>2009</v>
@@ -8472,7 +7997,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B21">
         <v>2010</v>
@@ -8513,7 +8038,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B22">
         <v>2011</v>
@@ -8554,7 +8079,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B23">
         <v>2012</v>
@@ -8595,7 +8120,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B24">
         <v>2013</v>
@@ -8636,7 +8161,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B25">
         <v>2014</v>
@@ -8677,7 +8202,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B26">
         <v>2015</v>
@@ -8718,7 +8243,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B27">
         <v>2016</v>
@@ -8759,7 +8284,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B28">
         <v>2017</v>
@@ -8800,7 +8325,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B29">
         <v>2018</v>
@@ -8841,7 +8366,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B30">
         <v>2019</v>
@@ -8882,7 +8407,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B31">
         <v>2020</v>
@@ -8923,7 +8448,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B32">
         <v>2021</v>
@@ -8964,7 +8489,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B33">
         <v>2022</v>
@@ -9074,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C11">
         <v>2020</v>
@@ -9115,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C12">
         <v>2025</v>
@@ -9156,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C13">
         <v>2030</v>
@@ -9197,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C14">
         <v>2035</v>
@@ -9238,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C15">
         <v>2040</v>
@@ -9279,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C16">
         <v>2045</v>
@@ -9320,7 +8845,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C17">
         <v>2050</v>
@@ -9361,7 +8886,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C18">
         <v>2020</v>
@@ -9402,7 +8927,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C19">
         <v>2025</v>
@@ -9443,7 +8968,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C20">
         <v>2030</v>
@@ -9484,7 +9009,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C21">
         <v>2035</v>
@@ -9525,7 +9050,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C22">
         <v>2040</v>
@@ -9566,7 +9091,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C23">
         <v>2045</v>
@@ -9607,7 +9132,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C24">
         <v>2050</v>
@@ -9648,7 +9173,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C25">
         <v>2020</v>
@@ -9689,7 +9214,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C26">
         <v>2025</v>
@@ -9730,7 +9255,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>2030</v>
@@ -9771,7 +9296,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C28">
         <v>2035</v>
@@ -9812,7 +9337,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>2040</v>
@@ -9853,7 +9378,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C30">
         <v>2045</v>
@@ -9894,7 +9419,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C31">
         <v>2050</v>
@@ -9935,7 +9460,7 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>2020</v>
@@ -9976,7 +9501,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C33">
         <v>2025</v>
@@ -10017,7 +9542,7 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C34">
         <v>2030</v>
@@ -10058,7 +9583,7 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C35">
         <v>2035</v>
@@ -10099,7 +9624,7 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C36">
         <v>2040</v>
@@ -10140,7 +9665,7 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C37">
         <v>2045</v>
@@ -10181,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C38">
         <v>2050</v>
@@ -10222,7 +9747,7 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C39">
         <v>2020</v>
@@ -10263,7 +9788,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C40">
         <v>2025</v>
@@ -10304,7 +9829,7 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C41">
         <v>2030</v>
@@ -10345,7 +9870,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C42">
         <v>2035</v>
@@ -10386,7 +9911,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C43">
         <v>2040</v>
@@ -10427,7 +9952,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C44">
         <v>2045</v>
@@ -10468,7 +9993,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>2050</v>
@@ -10509,7 +10034,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C46">
         <v>2020</v>
@@ -10550,7 +10075,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C47">
         <v>2025</v>
@@ -10591,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C48">
         <v>2030</v>
@@ -10632,7 +10157,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C49">
         <v>2035</v>
@@ -10673,7 +10198,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C50">
         <v>2040</v>
@@ -10714,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C51">
         <v>2045</v>
@@ -10755,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C52">
         <v>2050</v>
@@ -10796,7 +10321,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C53">
         <v>2020</v>
@@ -10837,7 +10362,7 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C54">
         <v>2025</v>
@@ -10878,7 +10403,7 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C55">
         <v>2030</v>
@@ -10919,7 +10444,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C56">
         <v>2035</v>
@@ -10960,7 +10485,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C57">
         <v>2040</v>
@@ -11001,7 +10526,7 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C58">
         <v>2045</v>
@@ -11042,7 +10567,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C59">
         <v>2050</v>
@@ -11083,7 +10608,7 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C60">
         <v>2020</v>
@@ -11124,7 +10649,7 @@
         <v>5</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C61">
         <v>2025</v>
@@ -11165,7 +10690,7 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C62">
         <v>2030</v>
@@ -11206,7 +10731,7 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C63">
         <v>2035</v>
@@ -11247,7 +10772,7 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C64">
         <v>2040</v>
@@ -11288,7 +10813,7 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C65">
         <v>2045</v>
@@ -11329,7 +10854,7 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>2050</v>
@@ -11370,7 +10895,7 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C67">
         <v>2020</v>
@@ -11411,7 +10936,7 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C68">
         <v>2025</v>
@@ -11452,7 +10977,7 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>2030</v>
@@ -11493,7 +11018,7 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>2035</v>
@@ -11534,7 +11059,7 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>2040</v>
@@ -11575,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C72">
         <v>2045</v>
@@ -11616,7 +11141,7 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C73">
         <v>2050</v>
@@ -11657,7 +11182,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C74">
         <v>2020</v>
@@ -11698,7 +11223,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C75">
         <v>2025</v>
@@ -11739,7 +11264,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C76">
         <v>2030</v>
@@ -11780,7 +11305,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C77">
         <v>2035</v>
@@ -11821,7 +11346,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C78">
         <v>2040</v>
@@ -11862,7 +11387,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C79">
         <v>2045</v>
@@ -11903,7 +11428,7 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C80">
         <v>2050</v>
@@ -11944,7 +11469,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C81">
         <v>2020</v>
@@ -11977,7 +11502,7 @@
         <v>1</v>
       </c>
       <c r="M81" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.45">
@@ -11985,7 +11510,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C82">
         <v>2025</v>
@@ -12018,7 +11543,7 @@
         <v>1</v>
       </c>
       <c r="M82" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.45">
@@ -12026,7 +11551,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C83">
         <v>2030</v>
@@ -12059,7 +11584,7 @@
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.45">
@@ -12067,7 +11592,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C84">
         <v>2035</v>
@@ -12100,7 +11625,7 @@
         <v>1</v>
       </c>
       <c r="M84" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.45">
@@ -12108,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C85">
         <v>2040</v>
@@ -12141,7 +11666,7 @@
         <v>1</v>
       </c>
       <c r="M85" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.45">
@@ -12149,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C86">
         <v>2045</v>
@@ -12182,7 +11707,7 @@
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.45">
@@ -12190,7 +11715,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C87">
         <v>2050</v>
@@ -12223,7 +11748,7 @@
         <v>1</v>
       </c>
       <c r="M87" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.45">
@@ -12231,7 +11756,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C88">
         <v>2020</v>
@@ -12264,7 +11789,7 @@
         <v>3</v>
       </c>
       <c r="M88" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.45">
@@ -12272,7 +11797,7 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C89">
         <v>2025</v>
@@ -12305,7 +11830,7 @@
         <v>3</v>
       </c>
       <c r="M89" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.45">
@@ -12313,7 +11838,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C90">
         <v>2030</v>
@@ -12346,7 +11871,7 @@
         <v>3</v>
       </c>
       <c r="M90" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.45">
@@ -12354,7 +11879,7 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C91">
         <v>2035</v>
@@ -12387,7 +11912,7 @@
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.45">
@@ -12395,7 +11920,7 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C92">
         <v>2040</v>
@@ -12428,7 +11953,7 @@
         <v>3</v>
       </c>
       <c r="M92" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.45">
@@ -12436,7 +11961,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C93">
         <v>2045</v>
@@ -12469,7 +11994,7 @@
         <v>3</v>
       </c>
       <c r="M93" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.45">
@@ -12477,7 +12002,7 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C94">
         <v>2050</v>
@@ -12510,7 +12035,7 @@
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.45">
@@ -12518,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C95">
         <v>2020</v>
@@ -12551,7 +12076,7 @@
         <v>6</v>
       </c>
       <c r="M95" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.45">
@@ -12559,7 +12084,7 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C96">
         <v>2025</v>
@@ -12592,7 +12117,7 @@
         <v>6</v>
       </c>
       <c r="M96" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.45">
@@ -12600,7 +12125,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C97">
         <v>2030</v>
@@ -12633,7 +12158,7 @@
         <v>6</v>
       </c>
       <c r="M97" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.45">
@@ -12641,7 +12166,7 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C98">
         <v>2035</v>
@@ -12674,7 +12199,7 @@
         <v>6</v>
       </c>
       <c r="M98" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.45">
@@ -12682,7 +12207,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C99">
         <v>2040</v>
@@ -12715,7 +12240,7 @@
         <v>6</v>
       </c>
       <c r="M99" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.45">
@@ -12723,7 +12248,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C100">
         <v>2045</v>
@@ -12756,7 +12281,7 @@
         <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.45">
@@ -12764,7 +12289,7 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C101">
         <v>2050</v>
@@ -12797,7 +12322,7 @@
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.45">
@@ -12805,7 +12330,7 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C102">
         <v>2020</v>
@@ -12838,7 +12363,7 @@
         <v>8</v>
       </c>
       <c r="M102" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.45">
@@ -12846,7 +12371,7 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C103">
         <v>2025</v>
@@ -12879,7 +12404,7 @@
         <v>8</v>
       </c>
       <c r="M103" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.45">
@@ -12887,7 +12412,7 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C104">
         <v>2030</v>
@@ -12920,7 +12445,7 @@
         <v>8</v>
       </c>
       <c r="M104" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.45">
@@ -12928,7 +12453,7 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C105">
         <v>2035</v>
@@ -12961,7 +12486,7 @@
         <v>8</v>
       </c>
       <c r="M105" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.45">
@@ -12969,7 +12494,7 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C106">
         <v>2040</v>
@@ -13002,7 +12527,7 @@
         <v>8</v>
       </c>
       <c r="M106" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.45">
@@ -13010,7 +12535,7 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C107">
         <v>2045</v>
@@ -13043,7 +12568,7 @@
         <v>8</v>
       </c>
       <c r="M107" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.45">
@@ -13051,7 +12576,7 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C108">
         <v>2050</v>
@@ -13084,7 +12609,7 @@
         <v>8</v>
       </c>
       <c r="M108" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.45">
@@ -13092,7 +12617,7 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C109">
         <v>2020</v>
@@ -13125,7 +12650,7 @@
         <v>10</v>
       </c>
       <c r="M109" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.45">
@@ -13133,7 +12658,7 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C110">
         <v>2025</v>
@@ -13166,7 +12691,7 @@
         <v>10</v>
       </c>
       <c r="M110" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.45">
@@ -13174,7 +12699,7 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C111">
         <v>2030</v>
@@ -13207,7 +12732,7 @@
         <v>10</v>
       </c>
       <c r="M111" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.45">
@@ -13215,7 +12740,7 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C112">
         <v>2035</v>
@@ -13248,7 +12773,7 @@
         <v>10</v>
       </c>
       <c r="M112" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.45">
@@ -13256,7 +12781,7 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C113">
         <v>2040</v>
@@ -13289,7 +12814,7 @@
         <v>10</v>
       </c>
       <c r="M113" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.45">
@@ -13297,7 +12822,7 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C114">
         <v>2045</v>
@@ -13330,7 +12855,7 @@
         <v>10</v>
       </c>
       <c r="M114" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.45">
@@ -13338,7 +12863,7 @@
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C115">
         <v>2050</v>
@@ -13371,7 +12896,7 @@
         <v>10</v>
       </c>
       <c r="M115" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.45">
@@ -13379,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C116">
         <v>2020</v>
@@ -13420,7 +12945,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C117">
         <v>2025</v>
@@ -13461,7 +12986,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C118">
         <v>2030</v>
@@ -13502,7 +13027,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C119">
         <v>2035</v>
@@ -13543,7 +13068,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C120">
         <v>2040</v>
@@ -13584,7 +13109,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C121">
         <v>2045</v>
@@ -13625,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C122">
         <v>2050</v>
@@ -13666,7 +13191,7 @@
         <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C123">
         <v>2020</v>
@@ -13707,7 +13232,7 @@
         <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C124">
         <v>2025</v>
@@ -13748,7 +13273,7 @@
         <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C125">
         <v>2030</v>
@@ -13789,7 +13314,7 @@
         <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C126">
         <v>2035</v>
@@ -13830,7 +13355,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C127">
         <v>2040</v>
@@ -13871,7 +13396,7 @@
         <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C128">
         <v>2045</v>
@@ -13912,7 +13437,7 @@
         <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C129">
         <v>2050</v>
@@ -13953,7 +13478,7 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C130">
         <v>2020</v>
@@ -13994,7 +13519,7 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C131">
         <v>2025</v>
@@ -14035,7 +13560,7 @@
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C132">
         <v>2030</v>
@@ -14076,7 +13601,7 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C133">
         <v>2035</v>
@@ -14117,7 +13642,7 @@
         <v>5</v>
       </c>
       <c r="B134" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C134">
         <v>2040</v>
@@ -14158,7 +13683,7 @@
         <v>5</v>
       </c>
       <c r="B135" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C135">
         <v>2045</v>
@@ -14199,7 +13724,7 @@
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C136">
         <v>2050</v>
@@ -14240,7 +13765,7 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C137">
         <v>2020</v>
@@ -14281,7 +13806,7 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C138">
         <v>2025</v>
@@ -14322,7 +13847,7 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C139">
         <v>2030</v>
@@ -14363,7 +13888,7 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C140">
         <v>2035</v>
@@ -14404,7 +13929,7 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C141">
         <v>2040</v>
@@ -14445,7 +13970,7 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C142">
         <v>2045</v>
@@ -14486,7 +14011,7 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C143">
         <v>2050</v>
@@ -14527,7 +14052,7 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C144">
         <v>2020</v>
@@ -14568,7 +14093,7 @@
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C145">
         <v>2025</v>
@@ -14609,7 +14134,7 @@
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C146">
         <v>2030</v>
@@ -14650,7 +14175,7 @@
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C147">
         <v>2035</v>
@@ -14691,7 +14216,7 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C148">
         <v>2040</v>
@@ -14732,7 +14257,7 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C149">
         <v>2045</v>
@@ -14773,7 +14298,7 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C150">
         <v>2050</v>
@@ -14814,7 +14339,7 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C151">
         <v>2020</v>
@@ -14855,7 +14380,7 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C152">
         <v>2025</v>
@@ -14896,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C153">
         <v>2030</v>
@@ -14937,7 +14462,7 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C154">
         <v>2035</v>
@@ -14978,7 +14503,7 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C155">
         <v>2040</v>
@@ -15019,7 +14544,7 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C156">
         <v>2045</v>
@@ -15060,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C157">
         <v>2050</v>
@@ -15101,7 +14626,7 @@
         <v>2</v>
       </c>
       <c r="B158" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C158">
         <v>2020</v>
@@ -15142,7 +14667,7 @@
         <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C159">
         <v>2025</v>
@@ -15183,7 +14708,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C160">
         <v>2030</v>
@@ -15224,7 +14749,7 @@
         <v>2</v>
       </c>
       <c r="B161" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C161">
         <v>2035</v>
@@ -15265,7 +14790,7 @@
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C162">
         <v>2040</v>
@@ -15306,7 +14831,7 @@
         <v>2</v>
       </c>
       <c r="B163" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C163">
         <v>2045</v>
@@ -15347,7 +14872,7 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C164">
         <v>2050</v>
@@ -15388,7 +14913,7 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C165">
         <v>2020</v>
@@ -15429,7 +14954,7 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C166">
         <v>2025</v>
@@ -15470,7 +14995,7 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C167">
         <v>2030</v>
@@ -15511,7 +15036,7 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C168">
         <v>2035</v>
@@ -15552,7 +15077,7 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C169">
         <v>2040</v>
@@ -15593,7 +15118,7 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C170">
         <v>2045</v>
@@ -15634,7 +15159,7 @@
         <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C171">
         <v>2050</v>
@@ -15675,7 +15200,7 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C172">
         <v>2020</v>
@@ -15716,7 +15241,7 @@
         <v>7</v>
       </c>
       <c r="B173" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C173">
         <v>2025</v>
@@ -15757,7 +15282,7 @@
         <v>7</v>
       </c>
       <c r="B174" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C174">
         <v>2030</v>
@@ -15798,7 +15323,7 @@
         <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C175">
         <v>2035</v>
@@ -15839,7 +15364,7 @@
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C176">
         <v>2040</v>
@@ -15880,7 +15405,7 @@
         <v>7</v>
       </c>
       <c r="B177" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C177">
         <v>2045</v>
@@ -15921,7 +15446,7 @@
         <v>7</v>
       </c>
       <c r="B178" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C178">
         <v>2050</v>
@@ -15962,7 +15487,7 @@
         <v>9</v>
       </c>
       <c r="B179" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C179">
         <v>2020</v>
@@ -16003,7 +15528,7 @@
         <v>9</v>
       </c>
       <c r="B180" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C180">
         <v>2025</v>
@@ -16044,7 +15569,7 @@
         <v>9</v>
       </c>
       <c r="B181" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C181">
         <v>2030</v>
@@ -16085,7 +15610,7 @@
         <v>9</v>
       </c>
       <c r="B182" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C182">
         <v>2035</v>
@@ -16126,7 +15651,7 @@
         <v>9</v>
       </c>
       <c r="B183" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C183">
         <v>2040</v>
@@ -16167,7 +15692,7 @@
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C184">
         <v>2045</v>
@@ -16208,7 +15733,7 @@
         <v>9</v>
       </c>
       <c r="B185" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C185">
         <v>2050</v>
@@ -16249,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C186">
         <v>2020</v>
@@ -16290,7 +15815,7 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C187">
         <v>2025</v>
@@ -16331,7 +15856,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C188">
         <v>2030</v>
@@ -16372,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C189">
         <v>2035</v>
@@ -16413,7 +15938,7 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C190">
         <v>2040</v>
@@ -16454,7 +15979,7 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C191">
         <v>2045</v>
@@ -16495,7 +16020,7 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C192">
         <v>2050</v>
@@ -16536,7 +16061,7 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C193">
         <v>2020</v>
@@ -16577,7 +16102,7 @@
         <v>2</v>
       </c>
       <c r="B194" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C194">
         <v>2025</v>
@@ -16618,7 +16143,7 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C195">
         <v>2030</v>
@@ -16659,7 +16184,7 @@
         <v>2</v>
       </c>
       <c r="B196" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C196">
         <v>2035</v>
@@ -16700,7 +16225,7 @@
         <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C197">
         <v>2040</v>
@@ -16741,7 +16266,7 @@
         <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C198">
         <v>2045</v>
@@ -16782,7 +16307,7 @@
         <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C199">
         <v>2050</v>
@@ -16823,7 +16348,7 @@
         <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C200">
         <v>2020</v>
@@ -16864,7 +16389,7 @@
         <v>5</v>
       </c>
       <c r="B201" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C201">
         <v>2025</v>
@@ -16905,7 +16430,7 @@
         <v>5</v>
       </c>
       <c r="B202" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C202">
         <v>2030</v>
@@ -16946,7 +16471,7 @@
         <v>5</v>
       </c>
       <c r="B203" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C203">
         <v>2035</v>
@@ -16987,7 +16512,7 @@
         <v>5</v>
       </c>
       <c r="B204" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C204">
         <v>2040</v>
@@ -17028,7 +16553,7 @@
         <v>5</v>
       </c>
       <c r="B205" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C205">
         <v>2045</v>
@@ -17069,7 +16594,7 @@
         <v>5</v>
       </c>
       <c r="B206" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C206">
         <v>2050</v>
@@ -17110,7 +16635,7 @@
         <v>7</v>
       </c>
       <c r="B207" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C207">
         <v>2020</v>
@@ -17151,7 +16676,7 @@
         <v>7</v>
       </c>
       <c r="B208" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C208">
         <v>2025</v>
@@ -17192,7 +16717,7 @@
         <v>7</v>
       </c>
       <c r="B209" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C209">
         <v>2030</v>
@@ -17233,7 +16758,7 @@
         <v>7</v>
       </c>
       <c r="B210" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C210">
         <v>2035</v>
@@ -17274,7 +16799,7 @@
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C211">
         <v>2040</v>
@@ -17315,7 +16840,7 @@
         <v>7</v>
       </c>
       <c r="B212" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C212">
         <v>2045</v>
@@ -17356,7 +16881,7 @@
         <v>7</v>
       </c>
       <c r="B213" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C213">
         <v>2050</v>
@@ -17397,7 +16922,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C214">
         <v>2020</v>
@@ -17438,7 +16963,7 @@
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C215">
         <v>2025</v>
@@ -17479,7 +17004,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C216">
         <v>2030</v>
@@ -17520,7 +17045,7 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C217">
         <v>2035</v>
@@ -17561,7 +17086,7 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C218">
         <v>2040</v>
@@ -17602,7 +17127,7 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C219">
         <v>2045</v>
@@ -17643,7 +17168,7 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C220">
         <v>2050</v>
@@ -17684,7 +17209,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C221">
         <v>2020</v>
@@ -17725,7 +17250,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C222">
         <v>2025</v>
@@ -17766,7 +17291,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C223">
         <v>2030</v>
@@ -17807,7 +17332,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C224">
         <v>2035</v>
@@ -17848,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C225">
         <v>2040</v>
@@ -17889,7 +17414,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C226">
         <v>2045</v>
@@ -17930,7 +17455,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C227">
         <v>2050</v>
@@ -17971,7 +17496,7 @@
         <v>2</v>
       </c>
       <c r="B228" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C228">
         <v>2020</v>
@@ -18012,7 +17537,7 @@
         <v>2</v>
       </c>
       <c r="B229" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C229">
         <v>2025</v>
@@ -18053,7 +17578,7 @@
         <v>2</v>
       </c>
       <c r="B230" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C230">
         <v>2030</v>
@@ -18094,7 +17619,7 @@
         <v>2</v>
       </c>
       <c r="B231" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C231">
         <v>2035</v>
@@ -18135,7 +17660,7 @@
         <v>2</v>
       </c>
       <c r="B232" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C232">
         <v>2040</v>
@@ -18176,7 +17701,7 @@
         <v>2</v>
       </c>
       <c r="B233" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C233">
         <v>2045</v>
@@ -18217,7 +17742,7 @@
         <v>2</v>
       </c>
       <c r="B234" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C234">
         <v>2050</v>
@@ -18258,7 +17783,7 @@
         <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C235">
         <v>2020</v>
@@ -18299,7 +17824,7 @@
         <v>5</v>
       </c>
       <c r="B236" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C236">
         <v>2025</v>
@@ -18340,7 +17865,7 @@
         <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C237">
         <v>2030</v>
@@ -18381,7 +17906,7 @@
         <v>5</v>
       </c>
       <c r="B238" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C238">
         <v>2035</v>
@@ -18422,7 +17947,7 @@
         <v>5</v>
       </c>
       <c r="B239" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C239">
         <v>2040</v>
@@ -18463,7 +17988,7 @@
         <v>5</v>
       </c>
       <c r="B240" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C240">
         <v>2045</v>
@@ -18504,7 +18029,7 @@
         <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C241">
         <v>2050</v>
@@ -18545,7 +18070,7 @@
         <v>7</v>
       </c>
       <c r="B242" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C242">
         <v>2020</v>
@@ -18586,7 +18111,7 @@
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C243">
         <v>2025</v>
@@ -18627,7 +18152,7 @@
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C244">
         <v>2030</v>
@@ -18668,7 +18193,7 @@
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C245">
         <v>2035</v>
@@ -18709,7 +18234,7 @@
         <v>7</v>
       </c>
       <c r="B246" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C246">
         <v>2040</v>
@@ -18750,7 +18275,7 @@
         <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C247">
         <v>2045</v>
@@ -18791,7 +18316,7 @@
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C248">
         <v>2050</v>
@@ -18832,7 +18357,7 @@
         <v>9</v>
       </c>
       <c r="B249" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C249">
         <v>2020</v>
@@ -18873,7 +18398,7 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C250">
         <v>2025</v>
@@ -18914,7 +18439,7 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C251">
         <v>2030</v>
@@ -18955,7 +18480,7 @@
         <v>9</v>
       </c>
       <c r="B252" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C252">
         <v>2035</v>
@@ -18996,7 +18521,7 @@
         <v>9</v>
       </c>
       <c r="B253" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C253">
         <v>2040</v>
@@ -19037,7 +18562,7 @@
         <v>9</v>
       </c>
       <c r="B254" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C254">
         <v>2045</v>
@@ -19078,7 +18603,7 @@
         <v>9</v>
       </c>
       <c r="B255" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C255">
         <v>2050</v>
@@ -19119,7 +18644,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C256">
         <v>2020</v>
@@ -19160,7 +18685,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C257">
         <v>2025</v>
@@ -19198,7 +18723,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C258">
         <v>2030</v>
@@ -19236,7 +18761,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C259">
         <v>2035</v>
@@ -19274,7 +18799,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C260">
         <v>2040</v>
@@ -19312,7 +18837,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C261">
         <v>2045</v>
@@ -19350,7 +18875,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C262">
         <v>2050</v>
@@ -19388,7 +18913,7 @@
         <v>2</v>
       </c>
       <c r="B263" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C263">
         <v>2020</v>
@@ -19429,7 +18954,7 @@
         <v>2</v>
       </c>
       <c r="B264" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C264">
         <v>2025</v>
@@ -19467,7 +18992,7 @@
         <v>2</v>
       </c>
       <c r="B265" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C265">
         <v>2030</v>
@@ -19505,7 +19030,7 @@
         <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C266">
         <v>2035</v>
@@ -19543,7 +19068,7 @@
         <v>2</v>
       </c>
       <c r="B267" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C267">
         <v>2040</v>
@@ -19581,7 +19106,7 @@
         <v>2</v>
       </c>
       <c r="B268" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C268">
         <v>2045</v>
@@ -19619,7 +19144,7 @@
         <v>2</v>
       </c>
       <c r="B269" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C269">
         <v>2050</v>
@@ -19657,7 +19182,7 @@
         <v>5</v>
       </c>
       <c r="B270" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C270">
         <v>2020</v>
@@ -19698,7 +19223,7 @@
         <v>5</v>
       </c>
       <c r="B271" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C271">
         <v>2025</v>
@@ -19736,7 +19261,7 @@
         <v>5</v>
       </c>
       <c r="B272" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C272">
         <v>2030</v>
@@ -19774,7 +19299,7 @@
         <v>5</v>
       </c>
       <c r="B273" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C273">
         <v>2035</v>
@@ -19812,7 +19337,7 @@
         <v>5</v>
       </c>
       <c r="B274" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C274">
         <v>2040</v>
@@ -19850,7 +19375,7 @@
         <v>5</v>
       </c>
       <c r="B275" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C275">
         <v>2045</v>
@@ -19888,7 +19413,7 @@
         <v>5</v>
       </c>
       <c r="B276" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C276">
         <v>2050</v>
@@ -19926,7 +19451,7 @@
         <v>7</v>
       </c>
       <c r="B277" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C277">
         <v>2020</v>
@@ -19967,7 +19492,7 @@
         <v>7</v>
       </c>
       <c r="B278" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C278">
         <v>2025</v>
@@ -20008,7 +19533,7 @@
         <v>7</v>
       </c>
       <c r="B279" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C279">
         <v>2030</v>
@@ -20049,7 +19574,7 @@
         <v>7</v>
       </c>
       <c r="B280" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C280">
         <v>2035</v>
@@ -20090,7 +19615,7 @@
         <v>7</v>
       </c>
       <c r="B281" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C281">
         <v>2040</v>
@@ -20131,7 +19656,7 @@
         <v>7</v>
       </c>
       <c r="B282" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C282">
         <v>2045</v>
@@ -20172,7 +19697,7 @@
         <v>7</v>
       </c>
       <c r="B283" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C283">
         <v>2050</v>
@@ -20213,7 +19738,7 @@
         <v>9</v>
       </c>
       <c r="B284" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C284">
         <v>2020</v>
@@ -20254,7 +19779,7 @@
         <v>9</v>
       </c>
       <c r="B285" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C285">
         <v>2025</v>
@@ -20295,7 +19820,7 @@
         <v>9</v>
       </c>
       <c r="B286" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C286">
         <v>2030</v>
@@ -20336,7 +19861,7 @@
         <v>9</v>
       </c>
       <c r="B287" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C287">
         <v>2035</v>
@@ -20377,7 +19902,7 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C288">
         <v>2040</v>
@@ -20418,7 +19943,7 @@
         <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C289">
         <v>2045</v>
@@ -20459,7 +19984,7 @@
         <v>9</v>
       </c>
       <c r="B290" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C290">
         <v>2050</v>
@@ -20500,7 +20025,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C291">
         <v>2020</v>
@@ -20541,7 +20066,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C292">
         <v>2025</v>
@@ -20579,7 +20104,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C293">
         <v>2030</v>
@@ -20617,7 +20142,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C294">
         <v>2035</v>
@@ -20655,7 +20180,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C295">
         <v>2040</v>
@@ -20693,7 +20218,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C296">
         <v>2045</v>
@@ -20731,7 +20256,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C297">
         <v>2050</v>
@@ -20769,7 +20294,7 @@
         <v>2</v>
       </c>
       <c r="B298" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C298">
         <v>2020</v>
@@ -20810,7 +20335,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C299">
         <v>2025</v>
@@ -20848,7 +20373,7 @@
         <v>2</v>
       </c>
       <c r="B300" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C300">
         <v>2030</v>
@@ -20886,7 +20411,7 @@
         <v>2</v>
       </c>
       <c r="B301" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C301">
         <v>2035</v>
@@ -20924,7 +20449,7 @@
         <v>2</v>
       </c>
       <c r="B302" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C302">
         <v>2040</v>
@@ -20962,7 +20487,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C303">
         <v>2045</v>
@@ -21000,7 +20525,7 @@
         <v>2</v>
       </c>
       <c r="B304" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C304">
         <v>2050</v>
@@ -21038,7 +20563,7 @@
         <v>5</v>
       </c>
       <c r="B305" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C305">
         <v>2020</v>
@@ -21079,7 +20604,7 @@
         <v>5</v>
       </c>
       <c r="B306" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C306">
         <v>2025</v>
@@ -21117,7 +20642,7 @@
         <v>5</v>
       </c>
       <c r="B307" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C307">
         <v>2030</v>
@@ -21155,7 +20680,7 @@
         <v>5</v>
       </c>
       <c r="B308" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C308">
         <v>2035</v>
@@ -21193,7 +20718,7 @@
         <v>5</v>
       </c>
       <c r="B309" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C309">
         <v>2040</v>
@@ -21231,7 +20756,7 @@
         <v>5</v>
       </c>
       <c r="B310" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C310">
         <v>2045</v>
@@ -21269,7 +20794,7 @@
         <v>5</v>
       </c>
       <c r="B311" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C311">
         <v>2050</v>
@@ -21307,7 +20832,7 @@
         <v>7</v>
       </c>
       <c r="B312" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C312">
         <v>2020</v>
@@ -21348,7 +20873,7 @@
         <v>7</v>
       </c>
       <c r="B313" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C313">
         <v>2025</v>
@@ -21389,7 +20914,7 @@
         <v>7</v>
       </c>
       <c r="B314" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C314">
         <v>2030</v>
@@ -21430,7 +20955,7 @@
         <v>7</v>
       </c>
       <c r="B315" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C315">
         <v>2035</v>
@@ -21471,7 +20996,7 @@
         <v>7</v>
       </c>
       <c r="B316" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C316">
         <v>2040</v>
@@ -21512,7 +21037,7 @@
         <v>7</v>
       </c>
       <c r="B317" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C317">
         <v>2045</v>
@@ -21553,7 +21078,7 @@
         <v>7</v>
       </c>
       <c r="B318" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C318">
         <v>2050</v>
@@ -21594,7 +21119,7 @@
         <v>9</v>
       </c>
       <c r="B319" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C319">
         <v>2020</v>
@@ -21635,7 +21160,7 @@
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C320">
         <v>2025</v>
@@ -21676,7 +21201,7 @@
         <v>9</v>
       </c>
       <c r="B321" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C321">
         <v>2030</v>
@@ -21717,7 +21242,7 @@
         <v>9</v>
       </c>
       <c r="B322" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C322">
         <v>2035</v>
@@ -21758,7 +21283,7 @@
         <v>9</v>
       </c>
       <c r="B323" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C323">
         <v>2040</v>
@@ -21799,7 +21324,7 @@
         <v>9</v>
       </c>
       <c r="B324" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C324">
         <v>2045</v>
@@ -21840,7 +21365,7 @@
         <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C325">
         <v>2050</v>
@@ -21881,7 +21406,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C326">
         <v>2020</v>
@@ -21922,7 +21447,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C327">
         <v>2025</v>
@@ -21963,7 +21488,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C328">
         <v>2030</v>
@@ -22004,7 +21529,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C329">
         <v>2035</v>
@@ -22045,7 +21570,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C330">
         <v>2040</v>
@@ -22086,7 +21611,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C331">
         <v>2045</v>
@@ -22127,7 +21652,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C332">
         <v>2050</v>
@@ -22168,7 +21693,7 @@
         <v>2</v>
       </c>
       <c r="B333" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C333">
         <v>2020</v>
@@ -22209,7 +21734,7 @@
         <v>2</v>
       </c>
       <c r="B334" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C334">
         <v>2025</v>
@@ -22250,7 +21775,7 @@
         <v>2</v>
       </c>
       <c r="B335" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C335">
         <v>2030</v>
@@ -22291,7 +21816,7 @@
         <v>2</v>
       </c>
       <c r="B336" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C336">
         <v>2035</v>
@@ -22332,7 +21857,7 @@
         <v>2</v>
       </c>
       <c r="B337" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C337">
         <v>2040</v>
@@ -22373,7 +21898,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C338">
         <v>2045</v>
@@ -22414,7 +21939,7 @@
         <v>2</v>
       </c>
       <c r="B339" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C339">
         <v>2050</v>
@@ -22455,7 +21980,7 @@
         <v>5</v>
       </c>
       <c r="B340" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C340">
         <v>2020</v>
@@ -22496,7 +22021,7 @@
         <v>5</v>
       </c>
       <c r="B341" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C341">
         <v>2025</v>
@@ -22537,7 +22062,7 @@
         <v>5</v>
       </c>
       <c r="B342" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C342">
         <v>2030</v>
@@ -22578,7 +22103,7 @@
         <v>5</v>
       </c>
       <c r="B343" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C343">
         <v>2035</v>
@@ -22619,7 +22144,7 @@
         <v>5</v>
       </c>
       <c r="B344" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C344">
         <v>2040</v>
@@ -22660,7 +22185,7 @@
         <v>5</v>
       </c>
       <c r="B345" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C345">
         <v>2045</v>
@@ -22701,7 +22226,7 @@
         <v>5</v>
       </c>
       <c r="B346" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C346">
         <v>2050</v>
@@ -22742,7 +22267,7 @@
         <v>7</v>
       </c>
       <c r="B347" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C347">
         <v>2020</v>
@@ -22783,7 +22308,7 @@
         <v>7</v>
       </c>
       <c r="B348" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C348">
         <v>2025</v>
@@ -22824,7 +22349,7 @@
         <v>7</v>
       </c>
       <c r="B349" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C349">
         <v>2030</v>
@@ -22865,7 +22390,7 @@
         <v>7</v>
       </c>
       <c r="B350" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C350">
         <v>2035</v>
@@ -22906,7 +22431,7 @@
         <v>7</v>
       </c>
       <c r="B351" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C351">
         <v>2040</v>
@@ -22947,7 +22472,7 @@
         <v>7</v>
       </c>
       <c r="B352" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C352">
         <v>2045</v>
@@ -22988,7 +22513,7 @@
         <v>7</v>
       </c>
       <c r="B353" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C353">
         <v>2050</v>
@@ -23029,7 +22554,7 @@
         <v>9</v>
       </c>
       <c r="B354" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C354">
         <v>2020</v>
@@ -23070,7 +22595,7 @@
         <v>9</v>
       </c>
       <c r="B355" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C355">
         <v>2025</v>
@@ -23111,7 +22636,7 @@
         <v>9</v>
       </c>
       <c r="B356" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C356">
         <v>2030</v>
@@ -23152,7 +22677,7 @@
         <v>9</v>
       </c>
       <c r="B357" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C357">
         <v>2035</v>
@@ -23193,7 +22718,7 @@
         <v>9</v>
       </c>
       <c r="B358" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C358">
         <v>2040</v>
@@ -23234,7 +22759,7 @@
         <v>9</v>
       </c>
       <c r="B359" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C359">
         <v>2045</v>
@@ -23275,7 +22800,7 @@
         <v>9</v>
       </c>
       <c r="B360" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C360">
         <v>2050</v>
@@ -23316,7 +22841,7 @@
         <v>0</v>
       </c>
       <c r="B361" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C361">
         <v>2020</v>
@@ -23357,7 +22882,7 @@
         <v>0</v>
       </c>
       <c r="B362" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C362">
         <v>2025</v>
@@ -23398,7 +22923,7 @@
         <v>0</v>
       </c>
       <c r="B363" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C363">
         <v>2030</v>
@@ -23439,7 +22964,7 @@
         <v>0</v>
       </c>
       <c r="B364" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C364">
         <v>2035</v>
@@ -23480,7 +23005,7 @@
         <v>0</v>
       </c>
       <c r="B365" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C365">
         <v>2040</v>
@@ -23521,7 +23046,7 @@
         <v>0</v>
       </c>
       <c r="B366" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C366">
         <v>2045</v>
@@ -23562,7 +23087,7 @@
         <v>0</v>
       </c>
       <c r="B367" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C367">
         <v>2050</v>
@@ -23603,7 +23128,7 @@
         <v>2</v>
       </c>
       <c r="B368" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C368">
         <v>2020</v>
@@ -23644,7 +23169,7 @@
         <v>2</v>
       </c>
       <c r="B369" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C369">
         <v>2025</v>
@@ -23685,7 +23210,7 @@
         <v>2</v>
       </c>
       <c r="B370" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C370">
         <v>2030</v>
@@ -23726,7 +23251,7 @@
         <v>2</v>
       </c>
       <c r="B371" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C371">
         <v>2035</v>
@@ -23767,7 +23292,7 @@
         <v>2</v>
       </c>
       <c r="B372" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C372">
         <v>2040</v>
@@ -23808,7 +23333,7 @@
         <v>2</v>
       </c>
       <c r="B373" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C373">
         <v>2045</v>
@@ -23849,7 +23374,7 @@
         <v>2</v>
       </c>
       <c r="B374" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C374">
         <v>2050</v>
@@ -23890,7 +23415,7 @@
         <v>5</v>
       </c>
       <c r="B375" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C375">
         <v>2020</v>
@@ -23931,7 +23456,7 @@
         <v>5</v>
       </c>
       <c r="B376" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C376">
         <v>2025</v>
@@ -23972,7 +23497,7 @@
         <v>5</v>
       </c>
       <c r="B377" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C377">
         <v>2030</v>
@@ -24013,7 +23538,7 @@
         <v>5</v>
       </c>
       <c r="B378" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C378">
         <v>2035</v>
@@ -24054,7 +23579,7 @@
         <v>5</v>
       </c>
       <c r="B379" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C379">
         <v>2040</v>
@@ -24095,7 +23620,7 @@
         <v>5</v>
       </c>
       <c r="B380" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C380">
         <v>2045</v>
@@ -24136,7 +23661,7 @@
         <v>5</v>
       </c>
       <c r="B381" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C381">
         <v>2050</v>
@@ -24177,7 +23702,7 @@
         <v>7</v>
       </c>
       <c r="B382" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C382">
         <v>2020</v>
@@ -24218,7 +23743,7 @@
         <v>7</v>
       </c>
       <c r="B383" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C383">
         <v>2025</v>
@@ -24259,7 +23784,7 @@
         <v>7</v>
       </c>
       <c r="B384" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C384">
         <v>2030</v>
@@ -24300,7 +23825,7 @@
         <v>7</v>
       </c>
       <c r="B385" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C385">
         <v>2035</v>
@@ -24341,7 +23866,7 @@
         <v>7</v>
       </c>
       <c r="B386" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C386">
         <v>2040</v>
@@ -24382,7 +23907,7 @@
         <v>7</v>
       </c>
       <c r="B387" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C387">
         <v>2045</v>
@@ -24423,7 +23948,7 @@
         <v>7</v>
       </c>
       <c r="B388" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C388">
         <v>2050</v>
@@ -24464,7 +23989,7 @@
         <v>9</v>
       </c>
       <c r="B389" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C389">
         <v>2020</v>
@@ -24505,7 +24030,7 @@
         <v>9</v>
       </c>
       <c r="B390" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C390">
         <v>2025</v>
@@ -24546,7 +24071,7 @@
         <v>9</v>
       </c>
       <c r="B391" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C391">
         <v>2030</v>
@@ -24587,7 +24112,7 @@
         <v>9</v>
       </c>
       <c r="B392" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C392">
         <v>2035</v>
@@ -24628,7 +24153,7 @@
         <v>9</v>
       </c>
       <c r="B393" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C393">
         <v>2040</v>
@@ -24669,7 +24194,7 @@
         <v>9</v>
       </c>
       <c r="B394" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C394">
         <v>2045</v>
@@ -24710,7 +24235,7 @@
         <v>9</v>
       </c>
       <c r="B395" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C395">
         <v>2050</v>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2372C176-A218-44D8-8D0B-D5B15CCBFE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3761D7-DA39-4764-86F8-883E80F8CB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3761D7-DA39-4764-86F8-883E80F8CB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD909FA-BEDA-49FB-84C9-F2285B7B356C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD909FA-BEDA-49FB-84C9-F2285B7B356C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F1DEAA-FBA2-4644-BC1A-F2E5B11B73C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
